--- a/Excel/Vlookup quetions new.xlsx
+++ b/Excel/Vlookup quetions new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC179D03-AB8F-453E-BF1D-A7CB52AE199A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701E19B6-988C-49E9-AB9B-88DE071B4507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8C07D453-D60F-43C8-AA7D-456D49938740}"/>
   </bookViews>
@@ -2221,7 +2221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{389EDA00-7BC1-40DE-968C-C03B001CBA19}">
-  <dimension ref="B2:Q56"/>
+  <dimension ref="B2:P56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="16.44140625" customWidth="1"/>
@@ -2231,7 +2231,7 @@
     <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="3"/>
       <c r="H2" s="5" t="s">
         <v>0</v>
@@ -2248,9 +2248,8 @@
       <c r="O2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="4"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>88</v>
       </c>
@@ -2264,15 +2263,15 @@
       <c r="N3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="6" t="e">
-        <f>VLOOKUP(N3,Q2:P6J26,1,0)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O3" s="6" t="str">
+        <f>VLOOKUP(N3,BusInfo[[BusNumber]:[BusType]],2,0)</f>
+        <v>Amit Sharma</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>89</v>
       </c>
@@ -2289,7 +2288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="H6" s="6">
         <v>5</v>
@@ -2301,17 +2300,17 @@
       <c r="N6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="O6" s="6" t="e">
-        <f>VLOOKUP(N6,Sheet2!B2:J26,3,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O6" s="6" t="str">
+        <f>VLOOKUP(N6,BusInfo[[BusNumber]:[BusType]],3,0)</f>
+        <v>Satara-Mumbai</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="H8" s="5" t="s">
         <v>0</v>
@@ -2326,7 +2325,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>91</v>
       </c>
@@ -2340,12 +2339,15 @@
       <c r="N9" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="6"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O9" s="6">
+        <f>VLOOKUP(N9,BusInfo[[BusNumber]:[BusType]],8,0)</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>92</v>
       </c>
@@ -2362,7 +2364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="H12" s="6">
         <v>3</v>
@@ -2374,14 +2376,17 @@
       <c r="N12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="O12" s="6"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O12" s="6" t="str">
+        <f>VLOOKUP(N12,BusInfo[[BusNumber]:[BusType]],4,0)</f>
+        <v>Mumbai</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="H14" s="5" t="s">
         <v>0</v>
@@ -2400,7 +2405,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>94</v>
       </c>
@@ -2414,10 +2419,16 @@
       <c r="N15" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="O15" s="6" t="str">
+        <f>VLOOKUP(N15,BusInfo[[BusNumber]:[BusType]],5,0)</f>
+        <v>Pune</v>
+      </c>
+      <c r="P15" s="6" t="str">
+        <f>VLOOKUP(N15,BusInfo[[BusNumber]:[BusType]],9,0)</f>
+        <v>AC</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
